--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Asha\Mammi\april\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Asha\Asha app\asha-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671B32ED-FC3B-4BD7-A7BA-BEAE1E9E3075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0207F273-C7EF-4741-8863-FC2E34439CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table ASHA 1" sheetId="5" r:id="rId1"/>
@@ -1924,26 +1924,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1954,41 +1934,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2008,22 +1972,58 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2339,128 +2339,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="48.75" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="90"/>
-      <c r="AA1" s="90"/>
-      <c r="AB1" s="90"/>
-      <c r="AC1" s="90"/>
-      <c r="AD1" s="90"/>
-      <c r="AE1" s="90"/>
-      <c r="AF1" s="90"/>
-      <c r="AG1" s="90"/>
-      <c r="AH1" s="91"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
+      <c r="AD1" s="101"/>
+      <c r="AE1" s="101"/>
+      <c r="AF1" s="101"/>
+      <c r="AG1" s="101"/>
+      <c r="AH1" s="102"/>
     </row>
     <row r="2" spans="1:35" ht="38.25" customHeight="1">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="96" t="s">
+      <c r="B2" s="97"/>
+      <c r="C2" s="95" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="96" t="s">
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="96" t="s">
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="95" t="s">
         <v>155</v>
       </c>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="93"/>
-      <c r="AB2" s="96" t="s">
+      <c r="W2" s="96"/>
+      <c r="X2" s="96"/>
+      <c r="Y2" s="96"/>
+      <c r="Z2" s="96"/>
+      <c r="AA2" s="97"/>
+      <c r="AB2" s="95" t="s">
         <v>154</v>
       </c>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="95"/>
-      <c r="AH2" s="97"/>
+      <c r="AC2" s="96"/>
+      <c r="AD2" s="96"/>
+      <c r="AE2" s="96"/>
+      <c r="AF2" s="96"/>
+      <c r="AG2" s="96"/>
+      <c r="AH2" s="99"/>
     </row>
     <row r="3" spans="1:35" ht="38.25" customHeight="1">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="98" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="95"/>
-      <c r="P3" s="95"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="95"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="95"/>
-      <c r="U3" s="93"/>
-      <c r="V3" s="96" t="s">
+      <c r="B3" s="97"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="W3" s="95"/>
-      <c r="X3" s="95"/>
-      <c r="Y3" s="95"/>
-      <c r="Z3" s="95"/>
-      <c r="AA3" s="95"/>
-      <c r="AB3" s="95"/>
-      <c r="AC3" s="95"/>
-      <c r="AD3" s="95"/>
-      <c r="AE3" s="95"/>
-      <c r="AF3" s="95"/>
-      <c r="AG3" s="95"/>
-      <c r="AH3" s="97"/>
+      <c r="W3" s="96"/>
+      <c r="X3" s="96"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="96"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="96"/>
+      <c r="AC3" s="96"/>
+      <c r="AD3" s="96"/>
+      <c r="AE3" s="96"/>
+      <c r="AF3" s="96"/>
+      <c r="AG3" s="96"/>
+      <c r="AH3" s="99"/>
     </row>
     <row r="4" spans="1:35" ht="28.5" customHeight="1">
       <c r="A4" s="31" t="s">
@@ -4353,42 +4353,42 @@
       </c>
     </row>
     <row r="22" spans="1:34" ht="31.2" customHeight="1">
-      <c r="A22" s="102" t="s">
+      <c r="A22" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="103"/>
-      <c r="M22" s="103"/>
-      <c r="N22" s="103"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="103"/>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="103"/>
-      <c r="S22" s="103"/>
-      <c r="T22" s="103"/>
-      <c r="U22" s="103"/>
-      <c r="V22" s="103"/>
-      <c r="W22" s="103"/>
-      <c r="X22" s="103"/>
-      <c r="Y22" s="103"/>
-      <c r="Z22" s="103"/>
-      <c r="AA22" s="103"/>
-      <c r="AB22" s="103"/>
-      <c r="AC22" s="103"/>
-      <c r="AD22" s="103"/>
-      <c r="AE22" s="103"/>
-      <c r="AF22" s="103"/>
-      <c r="AG22" s="103"/>
-      <c r="AH22" s="104"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="93"/>
+      <c r="R22" s="93"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="93"/>
+      <c r="U22" s="93"/>
+      <c r="V22" s="93"/>
+      <c r="W22" s="93"/>
+      <c r="X22" s="93"/>
+      <c r="Y22" s="93"/>
+      <c r="Z22" s="93"/>
+      <c r="AA22" s="93"/>
+      <c r="AB22" s="93"/>
+      <c r="AC22" s="93"/>
+      <c r="AD22" s="93"/>
+      <c r="AE22" s="93"/>
+      <c r="AF22" s="93"/>
+      <c r="AG22" s="93"/>
+      <c r="AH22" s="94"/>
     </row>
     <row r="23" spans="1:34" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
@@ -4589,24 +4589,24 @@
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
-      <c r="S28" s="98" t="s">
+      <c r="S28" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="T28" s="95"/>
-      <c r="U28" s="95"/>
-      <c r="V28" s="95"/>
-      <c r="W28" s="95"/>
-      <c r="X28" s="95"/>
-      <c r="Y28" s="95"/>
-      <c r="Z28" s="95"/>
-      <c r="AA28" s="95"/>
-      <c r="AB28" s="95"/>
-      <c r="AC28" s="95"/>
-      <c r="AD28" s="95"/>
-      <c r="AE28" s="95"/>
-      <c r="AF28" s="95"/>
-      <c r="AG28" s="95"/>
-      <c r="AH28" s="97"/>
+      <c r="T28" s="96"/>
+      <c r="U28" s="96"/>
+      <c r="V28" s="96"/>
+      <c r="W28" s="96"/>
+      <c r="X28" s="96"/>
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="96"/>
+      <c r="AA28" s="96"/>
+      <c r="AB28" s="96"/>
+      <c r="AC28" s="96"/>
+      <c r="AD28" s="96"/>
+      <c r="AE28" s="96"/>
+      <c r="AF28" s="96"/>
+      <c r="AG28" s="96"/>
+      <c r="AH28" s="99"/>
     </row>
     <row r="29" spans="1:34" ht="38.25" customHeight="1">
       <c r="A29" s="12"/>
@@ -4627,24 +4627,24 @@
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
-      <c r="S29" s="99" t="s">
+      <c r="S29" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="T29" s="100"/>
-      <c r="U29" s="100"/>
-      <c r="V29" s="100"/>
-      <c r="W29" s="100"/>
-      <c r="X29" s="100"/>
-      <c r="Y29" s="100"/>
-      <c r="Z29" s="100"/>
-      <c r="AA29" s="100"/>
-      <c r="AB29" s="100"/>
-      <c r="AC29" s="100"/>
-      <c r="AD29" s="100"/>
-      <c r="AE29" s="100"/>
-      <c r="AF29" s="100"/>
-      <c r="AG29" s="100"/>
-      <c r="AH29" s="101"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="90"/>
+      <c r="V29" s="90"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="90"/>
+      <c r="Z29" s="90"/>
+      <c r="AA29" s="90"/>
+      <c r="AB29" s="90"/>
+      <c r="AC29" s="90"/>
+      <c r="AD29" s="90"/>
+      <c r="AE29" s="90"/>
+      <c r="AF29" s="90"/>
+      <c r="AG29" s="90"/>
+      <c r="AH29" s="91"/>
     </row>
     <row r="30" spans="1:34" ht="15.75" customHeight="1">
       <c r="A30" s="14"/>
@@ -7204,6 +7204,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:U3"/>
+    <mergeCell ref="V3:AH3"/>
+    <mergeCell ref="S28:AH28"/>
     <mergeCell ref="S29:AH29"/>
     <mergeCell ref="A22:AH22"/>
     <mergeCell ref="M2:U2"/>
@@ -7211,11 +7216,6 @@
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="V2:AA2"/>
     <mergeCell ref="AB2:AH2"/>
-    <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:U3"/>
-    <mergeCell ref="V3:AH3"/>
-    <mergeCell ref="S28:AH28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.208661417322835" right="0.2" top="0.2" bottom="0.1" header="0" footer="0"/>
@@ -7244,18 +7244,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="35.25" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="91"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="102"/>
       <c r="K1" s="16"/>
       <c r="L1" s="16"/>
       <c r="M1" s="16"/>
@@ -7282,18 +7282,18 @@
       <c r="AH1" s="16"/>
     </row>
     <row r="2" spans="1:34" ht="36.75" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="97"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="99"/>
       <c r="K2" s="16"/>
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
@@ -7327,12 +7327,12 @@
       <c r="C3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="129" t="s">
+      <c r="D3" s="126" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
       <c r="J3" s="44"/>
@@ -7371,17 +7371,17 @@
       <c r="C4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="123" t="s">
+      <c r="D4" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="124" t="s">
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="110" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="95"/>
-      <c r="J4" s="97"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="99"/>
       <c r="K4" s="16"/>
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
@@ -7464,28 +7464,28 @@
       <c r="AH5" s="36"/>
     </row>
     <row r="6" spans="1:34" ht="48" customHeight="1">
-      <c r="A6" s="105">
+      <c r="A6" s="113">
         <v>1</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="125" t="s">
+      <c r="C6" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="107">
+      <c r="E6" s="122">
         <f>'Table ASHA 1'!AH5</f>
         <v>0</v>
       </c>
-      <c r="F6" s="116">
+      <c r="F6" s="125">
         <f>NORM!F3</f>
         <v>0</v>
       </c>
-      <c r="G6" s="109" t="e">
-        <f>E6*100/F6</f>
+      <c r="G6" s="111" t="e">
+        <f>E6*100/ROUND(F6,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H6" s="37" t="s">
@@ -7494,8 +7494,8 @@
       <c r="I6" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J6" s="110" t="e">
-        <f>IF((E6/F6&lt;75%),0,IF(E6/F6&gt;=100%,60,45))</f>
+      <c r="J6" s="116" t="e">
+        <f>IF(E6*100/ROUND(F6,0)&lt;75,0,IF(E6*100/ROUND(F6,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K6" s="16"/>
@@ -7524,20 +7524,20 @@
       <c r="AH6" s="16"/>
     </row>
     <row r="7" spans="1:34" ht="48" customHeight="1">
-      <c r="A7" s="106"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
+      <c r="A7" s="114"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
       <c r="H7" s="37" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="111"/>
+      <c r="J7" s="117"/>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
@@ -7564,28 +7564,28 @@
       <c r="AH7" s="16"/>
     </row>
     <row r="8" spans="1:34" ht="54" customHeight="1">
-      <c r="A8" s="105">
+      <c r="A8" s="113">
         <v>2</v>
       </c>
-      <c r="B8" s="114" t="s">
+      <c r="B8" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="115" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="117" t="s">
+      <c r="D8" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="107">
+      <c r="E8" s="122">
         <f>'Table ASHA 1'!AH6</f>
         <v>0</v>
       </c>
-      <c r="F8" s="109">
+      <c r="F8" s="111">
         <f>NORM!F4</f>
         <v>0</v>
       </c>
-      <c r="G8" s="109" t="e">
-        <f>((E8*100/F8)*"100%")</f>
+      <c r="G8" s="111" t="e">
+        <f>E8*100/ROUND(F8,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H8" s="37" t="s">
@@ -7594,8 +7594,8 @@
       <c r="I8" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="110" t="e">
-        <f>IF((E8/F8&lt;75%),0,IF(E8/F8&gt;=100%,60,45))</f>
+      <c r="J8" s="116" t="e">
+        <f>IF(E8*100/ROUND(F8,0)&lt;75,0,IF(E8*100/ROUND(F8,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K8" s="16"/>
@@ -7624,20 +7624,20 @@
       <c r="AH8" s="16"/>
     </row>
     <row r="9" spans="1:34" ht="79.5" customHeight="1">
-      <c r="A9" s="106"/>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
+      <c r="A9" s="114"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
       <c r="H9" s="37" t="s">
         <v>34</v>
       </c>
       <c r="I9" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J9" s="111"/>
+      <c r="J9" s="117"/>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
@@ -7664,28 +7664,28 @@
       <c r="AH9" s="16"/>
     </row>
     <row r="10" spans="1:34" ht="54" customHeight="1">
-      <c r="A10" s="105">
+      <c r="A10" s="113">
         <v>3</v>
       </c>
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="115" t="s">
+      <c r="D10" s="121" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="107">
+      <c r="E10" s="122">
         <f>'Table ASHA 1'!AH7</f>
         <v>0</v>
       </c>
-      <c r="F10" s="109">
+      <c r="F10" s="111">
         <f>NORM!F5</f>
         <v>0</v>
       </c>
-      <c r="G10" s="109" t="e">
-        <f>E10*100/F10</f>
+      <c r="G10" s="111" t="e">
+        <f>E10*100/ROUND(F10,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H10" s="37" t="s">
@@ -7694,8 +7694,8 @@
       <c r="I10" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J10" s="110" t="e">
-        <f>IF((E10/F10&lt;75%),0,IF(E10/F10&gt;=100%,60,45))</f>
+      <c r="J10" s="116" t="e">
+        <f>IF(E10*100/ROUND(F10,0)&lt;75,0,IF(E10*100/ROUND(F10,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K10" s="16"/>
@@ -7724,20 +7724,20 @@
       <c r="AH10" s="16"/>
     </row>
     <row r="11" spans="1:34" ht="54" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
+      <c r="A11" s="114"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
       <c r="H11" s="37" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="111"/>
+      <c r="J11" s="117"/>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
@@ -7764,28 +7764,28 @@
       <c r="AH11" s="16"/>
     </row>
     <row r="12" spans="1:34" ht="64.5" customHeight="1">
-      <c r="A12" s="105">
+      <c r="A12" s="113">
         <v>4</v>
       </c>
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="114" t="s">
+      <c r="C12" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="115" t="s">
+      <c r="D12" s="121" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="107">
+      <c r="E12" s="122">
         <f>'Table ASHA 1'!AH8</f>
         <v>0</v>
       </c>
-      <c r="F12" s="109">
+      <c r="F12" s="111">
         <f>NORM!F6</f>
         <v>0</v>
       </c>
-      <c r="G12" s="109" t="e">
-        <f>E12*100/F12</f>
+      <c r="G12" s="111" t="e">
+        <f>E12*100/ROUND(F12,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H12" s="37" t="s">
@@ -7794,8 +7794,8 @@
       <c r="I12" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J12" s="110" t="e">
-        <f>IF((E12/F12&lt;75%),0,IF(E12/F12&gt;=100%,60,45))</f>
+      <c r="J12" s="116" t="e">
+        <f>IF(E12*100/ROUND(F12,0)&lt;75,0,IF(E12*100/ROUND(F12,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K12" s="16"/>
@@ -7824,20 +7824,20 @@
       <c r="AH12" s="16"/>
     </row>
     <row r="13" spans="1:34" ht="64.5" customHeight="1">
-      <c r="A13" s="106"/>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="112"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
       <c r="H13" s="37" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="111"/>
+      <c r="J13" s="117"/>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
@@ -7864,28 +7864,28 @@
       <c r="AH13" s="16"/>
     </row>
     <row r="14" spans="1:34" ht="71.25" customHeight="1">
-      <c r="A14" s="105">
+      <c r="A14" s="113">
         <v>5</v>
       </c>
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="113" t="s">
+      <c r="C14" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="115" t="s">
+      <c r="D14" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="107">
+      <c r="E14" s="122">
         <f>'Table ASHA 1'!AH9</f>
         <v>0</v>
       </c>
-      <c r="F14" s="109">
+      <c r="F14" s="111">
         <f>NORM!F7</f>
         <v>0</v>
       </c>
-      <c r="G14" s="109" t="e">
-        <f>E14*100/F14</f>
+      <c r="G14" s="111" t="e">
+        <f>E14*100/ROUND(F14,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H14" s="37" t="s">
@@ -7894,8 +7894,8 @@
       <c r="I14" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="110" t="e">
-        <f>IF((E14/F14&lt;75%),0,IF(E14/F14&gt;=100%,60,45))</f>
+      <c r="J14" s="116" t="e">
+        <f>IF(E14*100/ROUND(F14,0)&lt;75,0,IF(E14*100/ROUND(F14,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K14" s="16"/>
@@ -7924,20 +7924,20 @@
       <c r="AH14" s="16"/>
     </row>
     <row r="15" spans="1:34" ht="71.25" customHeight="1">
-      <c r="A15" s="106"/>
-      <c r="B15" s="108"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="112"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
       <c r="H15" s="37" t="s">
         <v>43</v>
       </c>
       <c r="I15" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J15" s="111"/>
+      <c r="J15" s="117"/>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
@@ -7964,28 +7964,28 @@
       <c r="AH15" s="16"/>
     </row>
     <row r="16" spans="1:34" ht="71.25" customHeight="1">
-      <c r="A16" s="105">
+      <c r="A16" s="113">
         <v>6</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="114" t="s">
+      <c r="C16" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="115" t="s">
+      <c r="D16" s="121" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="107">
+      <c r="E16" s="122">
         <f>'Table ASHA 1'!AH10</f>
         <v>0</v>
       </c>
-      <c r="F16" s="109">
+      <c r="F16" s="111">
         <f>NORM!F8</f>
         <v>0</v>
       </c>
-      <c r="G16" s="109" t="e">
-        <f>E16*100/F16</f>
+      <c r="G16" s="111" t="e">
+        <f>E16*100/ROUND(F16,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H16" s="37" t="s">
@@ -7994,8 +7994,8 @@
       <c r="I16" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J16" s="110" t="e">
-        <f>IF((E16/F16&lt;75%),0,IF(E16/F16&gt;=100%,60,45))</f>
+      <c r="J16" s="116" t="e">
+        <f>IF(E16*100/ROUND(F16,0)&lt;75,0,IF(E16*100/ROUND(F16,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K16" s="16"/>
@@ -8024,20 +8024,20 @@
       <c r="AH16" s="16"/>
     </row>
     <row r="17" spans="1:34" ht="71.25" customHeight="1">
-      <c r="A17" s="106"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
       <c r="H17" s="37" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J17" s="111"/>
+      <c r="J17" s="117"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
@@ -8064,28 +8064,28 @@
       <c r="AH17" s="16"/>
     </row>
     <row r="18" spans="1:34" ht="63" customHeight="1">
-      <c r="A18" s="105">
+      <c r="A18" s="113">
         <v>7</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="114" t="s">
+      <c r="C18" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="121" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="107">
+      <c r="E18" s="122">
         <f>'Table ASHA 1'!AH11</f>
         <v>0</v>
       </c>
-      <c r="F18" s="109">
+      <c r="F18" s="111">
         <f>NORM!F9</f>
         <v>0</v>
       </c>
-      <c r="G18" s="109" t="e">
-        <f>E18*100/F18</f>
+      <c r="G18" s="111" t="e">
+        <f>E18*100/ROUND(F18,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H18" s="37" t="s">
@@ -8094,8 +8094,8 @@
       <c r="I18" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J18" s="110" t="e">
-        <f>IF((E18/F18&lt;75%),0,IF(E18/F18&gt;=100%,60,45))</f>
+      <c r="J18" s="116" t="e">
+        <f>IF(E18*100/ROUND(F18,0)&lt;75,0,IF(E18*100/ROUND(F18,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K18" s="16"/>
@@ -8124,20 +8124,20 @@
       <c r="AH18" s="16"/>
     </row>
     <row r="19" spans="1:34" ht="63" customHeight="1">
-      <c r="A19" s="106"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
       <c r="H19" s="37" t="s">
         <v>47</v>
       </c>
       <c r="I19" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J19" s="111"/>
+      <c r="J19" s="117"/>
       <c r="K19" s="16"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
@@ -8164,28 +8164,28 @@
       <c r="AH19" s="16"/>
     </row>
     <row r="20" spans="1:34" ht="88.5" customHeight="1">
-      <c r="A20" s="105">
+      <c r="A20" s="113">
         <v>8</v>
       </c>
-      <c r="B20" s="115" t="s">
+      <c r="B20" s="121" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="114" t="s">
+      <c r="C20" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="115" t="s">
+      <c r="D20" s="121" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="107">
+      <c r="E20" s="122">
         <f>'Table ASHA 1'!AH12</f>
         <v>0</v>
       </c>
-      <c r="F20" s="109">
+      <c r="F20" s="111">
         <f>NORM!F10</f>
         <v>0</v>
       </c>
-      <c r="G20" s="109" t="e">
-        <f>E20*100/F20</f>
+      <c r="G20" s="111" t="e">
+        <f>E20*100/ROUND(F20,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H20" s="37" t="s">
@@ -8194,8 +8194,8 @@
       <c r="I20" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="110" t="e">
-        <f>IF((E20/F20&lt;75%),0,IF(E20/F20&gt;=100%,60,45))</f>
+      <c r="J20" s="116" t="e">
+        <f>IF(E20*100/ROUND(F20,0)&lt;75,0,IF(E20*100/ROUND(F20,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K20" s="16"/>
@@ -8224,20 +8224,20 @@
       <c r="AH20" s="16"/>
     </row>
     <row r="21" spans="1:34" ht="88.5" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="112"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
       <c r="H21" s="37" t="s">
         <v>49</v>
       </c>
       <c r="I21" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="111"/>
+      <c r="J21" s="117"/>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
@@ -8264,28 +8264,28 @@
       <c r="AH21" s="16"/>
     </row>
     <row r="22" spans="1:34" ht="58.5" customHeight="1">
-      <c r="A22" s="105">
+      <c r="A22" s="113">
         <v>9</v>
       </c>
-      <c r="B22" s="114" t="s">
+      <c r="B22" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="114" t="s">
+      <c r="C22" s="115" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="115" t="s">
+      <c r="D22" s="121" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="107">
+      <c r="E22" s="122">
         <f>'Table ASHA 1'!AH13</f>
         <v>0</v>
       </c>
-      <c r="F22" s="109">
+      <c r="F22" s="111">
         <f>NORM!F11</f>
         <v>0</v>
       </c>
-      <c r="G22" s="109" t="e">
-        <f>E22*100/F22</f>
+      <c r="G22" s="111" t="e">
+        <f>E22*100/ROUND(F22,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H22" s="37" t="s">
@@ -8294,8 +8294,8 @@
       <c r="I22" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="110" t="e">
-        <f>IF((E22/F22&lt;75%),0,IF(E22/F22&gt;=100%,60,45))</f>
+      <c r="J22" s="116" t="e">
+        <f>IF(E22*100/ROUND(F22,0)&lt;75,0,IF(E22*100/ROUND(F22,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K22" s="16"/>
@@ -8324,20 +8324,20 @@
       <c r="AH22" s="16"/>
     </row>
     <row r="23" spans="1:34" ht="58.5" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="108"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
       <c r="H23" s="37" t="s">
         <v>47</v>
       </c>
       <c r="I23" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J23" s="111"/>
+      <c r="J23" s="117"/>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
@@ -8364,28 +8364,28 @@
       <c r="AH23" s="16"/>
     </row>
     <row r="24" spans="1:34" ht="58.5" customHeight="1">
-      <c r="A24" s="105">
+      <c r="A24" s="113">
         <v>10</v>
       </c>
-      <c r="B24" s="114" t="s">
+      <c r="B24" s="115" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="114" t="s">
+      <c r="C24" s="115" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="115" t="s">
+      <c r="D24" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="107">
+      <c r="E24" s="122">
         <f>'Table ASHA 1'!AH14</f>
         <v>0</v>
       </c>
-      <c r="F24" s="109">
+      <c r="F24" s="111">
         <f>NORM!F13</f>
         <v>0</v>
       </c>
-      <c r="G24" s="109" t="e">
-        <f>E24*100/F24</f>
+      <c r="G24" s="111" t="e">
+        <f>E24*100/ROUND(F24,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -8394,8 +8394,8 @@
       <c r="I24" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="110" t="e">
-        <f>IF((E24/F24&lt;75%),0,IF(E24/F24&gt;=100%,60,45))</f>
+      <c r="J24" s="116" t="e">
+        <f>IF(E24*100/ROUND(F24,0)&lt;75,0,IF(E24*100/ROUND(F24,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="16"/>
@@ -8424,20 +8424,20 @@
       <c r="AH24" s="16"/>
     </row>
     <row r="25" spans="1:34" ht="58.5" customHeight="1">
-      <c r="A25" s="106"/>
-      <c r="B25" s="108"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
+      <c r="A25" s="114"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="37" t="s">
         <v>52</v>
       </c>
       <c r="I25" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J25" s="111"/>
+      <c r="J25" s="117"/>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
@@ -8464,28 +8464,28 @@
       <c r="AH25" s="16"/>
     </row>
     <row r="26" spans="1:34" ht="72" customHeight="1">
-      <c r="A26" s="105">
+      <c r="A26" s="113">
         <v>11</v>
       </c>
-      <c r="B26" s="114" t="s">
+      <c r="B26" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="113" t="s">
+      <c r="C26" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="115" t="s">
+      <c r="D26" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="107">
+      <c r="E26" s="122">
         <f>'Table ASHA 1'!AH15</f>
         <v>0</v>
       </c>
-      <c r="F26" s="109">
+      <c r="F26" s="111">
         <f>NORM!F14</f>
         <v>0</v>
       </c>
-      <c r="G26" s="109" t="e">
-        <f>E26*100/F26</f>
+      <c r="G26" s="111" t="e">
+        <f>E26*100/ROUND(F26,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H26" s="37" t="s">
@@ -8494,8 +8494,8 @@
       <c r="I26" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J26" s="110" t="e">
-        <f>IF((E26/F26&lt;75%),0,IF(E26/F26&gt;=100%,60,45))</f>
+      <c r="J26" s="116" t="e">
+        <f>IF(E26*100/ROUND(F26,0)&lt;75,0,IF(E26*100/ROUND(F26,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="16"/>
@@ -8524,20 +8524,20 @@
       <c r="AH26" s="16"/>
     </row>
     <row r="27" spans="1:34" ht="72" customHeight="1">
-      <c r="A27" s="106"/>
-      <c r="B27" s="108"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="108"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="108"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
       <c r="H27" s="37" t="s">
         <v>55</v>
       </c>
       <c r="I27" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J27" s="111"/>
+      <c r="J27" s="117"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
@@ -8564,28 +8564,28 @@
       <c r="AH27" s="16"/>
     </row>
     <row r="28" spans="1:34" ht="57" customHeight="1">
-      <c r="A28" s="105">
+      <c r="A28" s="113">
         <v>12</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C28" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="115" t="s">
+      <c r="D28" s="121" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="107">
+      <c r="E28" s="122">
         <f>'Table ASHA 1'!AH16</f>
         <v>0</v>
       </c>
-      <c r="F28" s="109">
+      <c r="F28" s="111">
         <f>NORM!F15</f>
         <v>52</v>
       </c>
-      <c r="G28" s="109">
-        <f>(E28*100/F28)</f>
+      <c r="G28" s="111">
+        <f>E28*100/ROUND(F28,0)</f>
         <v>0</v>
       </c>
       <c r="H28" s="37" t="s">
@@ -8594,8 +8594,8 @@
       <c r="I28" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="110">
-        <f>IF((E28/F28&lt;75%),0,IF(E28/F28&gt;=100%,60,45))</f>
+      <c r="J28" s="116">
+        <f>IF(E28*100/ROUND(F28,0)&lt;75,0,IF(E28*100/ROUND(F28,0)&gt;=100,60,45))</f>
         <v>0</v>
       </c>
       <c r="K28" s="16"/>
@@ -8624,20 +8624,20 @@
       <c r="AH28" s="16"/>
     </row>
     <row r="29" spans="1:34" ht="57" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="108"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="108"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
       <c r="H29" s="37" t="s">
         <v>59</v>
       </c>
       <c r="I29" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J29" s="111"/>
+      <c r="J29" s="117"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
@@ -8664,28 +8664,28 @@
       <c r="AH29" s="16"/>
     </row>
     <row r="30" spans="1:34" ht="90" customHeight="1">
-      <c r="A30" s="105">
+      <c r="A30" s="113">
         <v>13</v>
       </c>
-      <c r="B30" s="112" t="s">
+      <c r="B30" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="113" t="s">
+      <c r="C30" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="115" t="s">
+      <c r="D30" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="107">
+      <c r="E30" s="122">
         <f>'Table ASHA 1'!AH17</f>
         <v>0</v>
       </c>
-      <c r="F30" s="109">
+      <c r="F30" s="111">
         <f>NORM!F16</f>
         <v>5</v>
       </c>
-      <c r="G30" s="109">
-        <f>(E30*100/F30)</f>
+      <c r="G30" s="111">
+        <f>E30*100/ROUND(F30,0)</f>
         <v>0</v>
       </c>
       <c r="H30" s="37" t="s">
@@ -8694,8 +8694,8 @@
       <c r="I30" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="110">
-        <f>IF((E30/F30&lt;75%),0,IF(E30/F30&gt;=100%,60,45))</f>
+      <c r="J30" s="116">
+        <f>IF(E30*100/ROUND(F30,0)&lt;75,0,IF(E30*100/ROUND(F30,0)&gt;=100,60,45))</f>
         <v>0</v>
       </c>
       <c r="K30" s="16"/>
@@ -8724,20 +8724,20 @@
       <c r="AH30" s="16"/>
     </row>
     <row r="31" spans="1:34" ht="90" customHeight="1">
-      <c r="A31" s="106"/>
-      <c r="B31" s="108"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
+      <c r="A31" s="114"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
       <c r="H31" s="37" t="s">
         <v>63</v>
       </c>
       <c r="I31" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J31" s="111"/>
+      <c r="J31" s="117"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
@@ -8785,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="39">
-        <f t="shared" ref="G32:G33" si="0">(E32*100/F32)</f>
+        <f>E32*100/ROUND(F32,0)</f>
         <v>0</v>
       </c>
       <c r="H32" s="37" t="s">
@@ -8795,7 +8795,7 @@
         <v>104</v>
       </c>
       <c r="J32" s="40">
-        <f t="shared" ref="J32:J33" si="1">IF(E32&gt;=1,50,0)</f>
+        <f>IF(ROUND(E32,0)&gt;=1,50,0)</f>
         <v>0</v>
       </c>
       <c r="K32" s="16"/>
@@ -8845,7 +8845,7 @@
         <v>3</v>
       </c>
       <c r="G33" s="39">
-        <f t="shared" si="0"/>
+        <f>E33*100/ROUND(F33,0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="37" t="s">
@@ -8855,7 +8855,7 @@
         <v>104</v>
       </c>
       <c r="J33" s="40">
-        <f t="shared" si="1"/>
+        <f>IF(ROUND(E33,0)&gt;=1,50,0)</f>
         <v>0</v>
       </c>
       <c r="K33" s="16"/>
@@ -8884,28 +8884,28 @@
       <c r="AH33" s="16"/>
     </row>
     <row r="34" spans="1:34" ht="59.25" customHeight="1">
-      <c r="A34" s="105">
+      <c r="A34" s="113">
         <v>16</v>
       </c>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="113" t="s">
+      <c r="C34" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="115" t="s">
+      <c r="D34" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="E34" s="107">
+      <c r="E34" s="122">
         <f>'Table ASHA 1'!AH20</f>
         <v>0</v>
       </c>
-      <c r="F34" s="109">
+      <c r="F34" s="111">
         <f>NORM!F19</f>
         <v>0</v>
       </c>
-      <c r="G34" s="109" t="e">
-        <f>E34*100/F34</f>
+      <c r="G34" s="111" t="e">
+        <f>E34*100/ROUND(F34,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H34" s="37" t="s">
@@ -8914,8 +8914,8 @@
       <c r="I34" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="110" t="e">
-        <f>IF((E34/F34&lt;75%),0,IF(E34/F34&gt;=100%,60,45))</f>
+      <c r="J34" s="116" t="e">
+        <f>IF(E34*100/ROUND(F34,0)&lt;75,0,IF(E34*100/ROUND(F34,0)&gt;=100,60,45))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="16"/>
@@ -8944,20 +8944,20 @@
       <c r="AH34" s="16"/>
     </row>
     <row r="35" spans="1:34" ht="59.25" customHeight="1">
-      <c r="A35" s="106"/>
-      <c r="B35" s="108"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
+      <c r="A35" s="114"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="112"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="112"/>
       <c r="H35" s="37" t="s">
         <v>72</v>
       </c>
       <c r="I35" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="111"/>
+      <c r="J35" s="117"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
@@ -8984,28 +8984,28 @@
       <c r="AH35" s="16"/>
     </row>
     <row r="36" spans="1:34" ht="59.25" customHeight="1">
-      <c r="A36" s="126">
+      <c r="A36" s="120">
         <v>17</v>
       </c>
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="114" t="s">
+      <c r="C36" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="115" t="s">
+      <c r="D36" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="107">
+      <c r="E36" s="122">
         <f>'Table ASHA 1'!AH21</f>
         <v>0</v>
       </c>
-      <c r="F36" s="109">
+      <c r="F36" s="111">
         <f>NORM!F20</f>
         <v>220</v>
       </c>
-      <c r="G36" s="109">
-        <f>(E36*100/F36)</f>
+      <c r="G36" s="111">
+        <f>E36*100/ROUND(F36,0)</f>
         <v>0</v>
       </c>
       <c r="H36" s="37" t="s">
@@ -9014,8 +9014,8 @@
       <c r="I36" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="110">
-        <f>IF((E36/F36&lt;75%),0,IF(E36/F36&gt;=100%,60,45))</f>
+      <c r="J36" s="116">
+        <f>IF(E36*100/ROUND(F36,0)&lt;75,0,IF(E36*100/ROUND(F36,0)&gt;=100,60,45))</f>
         <v>0</v>
       </c>
       <c r="K36" s="16"/>
@@ -9044,20 +9044,20 @@
       <c r="AH36" s="16"/>
     </row>
     <row r="37" spans="1:34" ht="59.25" customHeight="1">
-      <c r="A37" s="108"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
+      <c r="A37" s="112"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="112"/>
       <c r="H37" s="37" t="s">
         <v>74</v>
       </c>
       <c r="I37" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J37" s="111"/>
+      <c r="J37" s="117"/>
       <c r="K37" s="16"/>
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
@@ -9123,18 +9123,18 @@
       <c r="AH38" s="16"/>
     </row>
     <row r="39" spans="1:34" ht="33" customHeight="1">
-      <c r="A39" s="119" t="s">
+      <c r="A39" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="120"/>
-      <c r="C39" s="120"/>
-      <c r="D39" s="120"/>
-      <c r="E39" s="120"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="120"/>
-      <c r="H39" s="120"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="121"/>
+      <c r="B39" s="106"/>
+      <c r="C39" s="106"/>
+      <c r="D39" s="106"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="106"/>
+      <c r="G39" s="106"/>
+      <c r="H39" s="106"/>
+      <c r="I39" s="106"/>
+      <c r="J39" s="107"/>
       <c r="K39" s="83"/>
       <c r="L39" s="83"/>
       <c r="M39" s="83"/>
@@ -9275,12 +9275,12 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="98" t="s">
+      <c r="G43" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="H43" s="95"/>
-      <c r="I43" s="95"/>
-      <c r="J43" s="93"/>
+      <c r="H43" s="96"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="97"/>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
@@ -9313,12 +9313,12 @@
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
-      <c r="G44" s="98" t="s">
+      <c r="G44" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="H44" s="95"/>
-      <c r="I44" s="95"/>
-      <c r="J44" s="93"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="97"/>
       <c r="K44" s="50"/>
       <c r="L44" s="50"/>
       <c r="M44" s="50"/>
@@ -11362,6 +11362,110 @@
     </row>
   </sheetData>
   <mergeCells count="128">
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="D4:G4"/>
@@ -11386,110 +11490,6 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.35" bottom="0.1" header="0" footer="0"/>
@@ -11520,16 +11520,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="51" customHeight="1">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="129" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
       <c r="I1" s="52"/>
       <c r="J1" s="52"/>
       <c r="K1" s="52"/>
